--- a/artfynd/A 7260-2026 artfynd.xlsx
+++ b/artfynd/A 7260-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132821205</v>
+        <v>132821201</v>
       </c>
       <c r="B2" t="n">
-        <v>97997</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569370</v>
+        <v>569463</v>
       </c>
       <c r="R2" t="n">
-        <v>7208004</v>
+        <v>7207974</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132821198</v>
+        <v>132821202</v>
       </c>
       <c r="B3" t="n">
-        <v>97997</v>
+        <v>91988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569437</v>
+        <v>569459</v>
       </c>
       <c r="R3" t="n">
-        <v>7207874</v>
+        <v>7207976</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132821204</v>
+        <v>132821195</v>
       </c>
       <c r="B4" t="n">
-        <v>57136</v>
+        <v>80489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,43 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mittibergbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569369</v>
+        <v>569429</v>
       </c>
       <c r="R4" t="n">
-        <v>7208002</v>
+        <v>7207635</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -968,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,7 +999,7 @@
         <v>132821197</v>
       </c>
       <c r="B5" t="n">
-        <v>80440</v>
+        <v>80489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,14 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132821203</v>
+        <v>132821196</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1147,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569396</v>
+        <v>569414</v>
       </c>
       <c r="R6" t="n">
-        <v>7207985</v>
+        <v>7207636</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1182,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1192,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,11 +1213,11 @@
         <v>132821199</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1326,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132821195</v>
+        <v>132821203</v>
       </c>
       <c r="B8" t="n">
-        <v>80440</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569429</v>
+        <v>569396</v>
       </c>
       <c r="R8" t="n">
-        <v>7207635</v>
+        <v>7207985</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1396,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1406,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132821206</v>
+        <v>132821207</v>
       </c>
       <c r="B9" t="n">
-        <v>98003</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1468,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569247</v>
+        <v>569214</v>
       </c>
       <c r="R9" t="n">
-        <v>7207948</v>
+        <v>7207861</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1503,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1513,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132821194</v>
+        <v>132821208</v>
       </c>
       <c r="B10" t="n">
-        <v>80475</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1575,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569429</v>
+        <v>569209</v>
       </c>
       <c r="R10" t="n">
-        <v>7207635</v>
+        <v>7207857</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1610,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1620,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132821196</v>
+        <v>132821194</v>
       </c>
       <c r="B11" t="n">
-        <v>79334</v>
+        <v>80500</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1682,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569414</v>
+        <v>569429</v>
       </c>
       <c r="R11" t="n">
-        <v>7207636</v>
+        <v>7207635</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1717,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1727,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1754,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132821200</v>
+        <v>132821204</v>
       </c>
       <c r="B12" t="n">
-        <v>106245</v>
+        <v>57153</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,34 +1756,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mittibergbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569452</v>
+        <v>569369</v>
       </c>
       <c r="R12" t="n">
-        <v>7207907</v>
+        <v>7208002</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,32 +1861,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132821208</v>
+        <v>132821200</v>
       </c>
       <c r="B13" t="n">
-        <v>79334</v>
+        <v>106309</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569209</v>
+        <v>569452</v>
       </c>
       <c r="R13" t="n">
-        <v>7207857</v>
+        <v>7207907</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,6 +1965,327 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132821206</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mittibergbäcken, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>569247</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7207948</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132821198</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mittibergbäcken, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>569437</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7207874</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132821205</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mittibergbäcken, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>569370</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7208004</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
